--- a/data/trans_orig/P16A_n_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas</t>
+          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,57 +716,57 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,78</t>
+          <t>0,55; 0,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,44</t>
+          <t>0,96; 1,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,01</t>
+          <t>0,77; 1,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,4</t>
+          <t>1,07; 1,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,27</t>
+          <t>0,91; 1,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,77</t>
+          <t>1,4; 1,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,54</t>
+          <t>1,2; 1,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 1,68</t>
+          <t>1,4; 1,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 0,99</t>
+          <t>0,77; 0,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,51</t>
+          <t>1,22; 1,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,25</t>
+          <t>1,02; 1,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,52 +856,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,74</t>
+          <t>0,55; 0,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,32</t>
+          <t>0,98; 1,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,01</t>
+          <t>0,78; 1,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,22</t>
+          <t>0,9; 1,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,35</t>
+          <t>1,08; 1,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,83</t>
+          <t>1,49; 1,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,54</t>
+          <t>1,26; 1,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 1,76</t>
+          <t>1,46; 1,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,01</t>
+          <t>0,84; 1,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,52</t>
+          <t>1,28; 1,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,45</t>
+          <t>1,22; 1,44</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,69</t>
+          <t>0,5; 0,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,27</t>
+          <t>0,95; 1,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,22 +1011,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,72</t>
+          <t>1,32; 1,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,14</t>
+          <t>0,91; 1,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 1,79</t>
+          <t>1,45; 1,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,32</t>
+          <t>1,03; 1,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,48</t>
+          <t>1,26; 1,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,12</t>
+          <t>0,93; 1,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 1,92</t>
+          <t>1,6; 1,9</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,77</t>
+          <t>0,57; 0,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,14</t>
+          <t>0,85; 1,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,33</t>
+          <t>1,03; 1,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,65</t>
+          <t>1,16; 1,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,24</t>
+          <t>0,99; 1,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,16</t>
+          <t>1,74; 2,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,01</t>
+          <t>1,63; 2,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 1,82</t>
+          <t>1,25; 1,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,6</t>
+          <t>1,34; 1,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,62</t>
+          <t>1,38; 1,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,66</t>
+          <t>1,27; 1,66</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,88</t>
+          <t>0,61; 0,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,44</t>
+          <t>0,98; 1,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,97</t>
+          <t>0,64; 0,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,39</t>
+          <t>0,99; 1,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,58</t>
+          <t>1,14; 1,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 2,78</t>
+          <t>2,14; 2,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,79</t>
+          <t>1,35; 1,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,05</t>
+          <t>0,85; 2,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,19</t>
+          <t>0,91; 1,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,02</t>
+          <t>1,6; 2,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,32</t>
+          <t>1,04; 1,35</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,66</t>
+          <t>1,01; 1,68</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,79</t>
+          <t>0,55; 0,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,35</t>
+          <t>1,03; 1,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,06</t>
+          <t>0,72; 1,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,99</t>
+          <t>1,54; 1,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,33</t>
+          <t>1,01; 1,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,85</t>
+          <t>1,51; 1,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,63</t>
+          <t>1,19; 1,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,27</t>
+          <t>1,84; 2,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,01</t>
+          <t>0,81; 1,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,56</t>
+          <t>1,32; 1,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,28</t>
+          <t>1,0; 1,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,05</t>
+          <t>1,73; 2,06</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,87</t>
+          <t>0,64; 0,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,44</t>
+          <t>1,16; 1,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,63</t>
+          <t>1,38; 1,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,34</t>
+          <t>1,11; 1,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,14</t>
+          <t>1,85; 3,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,33</t>
+          <t>1,17; 1,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,14</t>
+          <t>0,97; 1,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,76</t>
+          <t>1,57; 2,66</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,92</t>
+          <t>0,72; 0,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,32 +1711,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,02</t>
+          <t>0,33; 1,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,31</t>
+          <t>1,07; 1,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,51</t>
+          <t>1,23; 1,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 1,55</t>
+          <t>1,32; 1,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 1,72</t>
+          <t>1,42; 1,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,11</t>
+          <t>0,96; 1,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,27</t>
+          <t>1,1; 1,25</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,3</t>
+          <t>0,66; 1,31</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,75</t>
+          <t>0,68; 0,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,88; 0,96</t>
+          <t>0,87; 0,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,27</t>
+          <t>0,89; 1,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,19</t>
+          <t>1,1; 1,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,45</t>
+          <t>1,34; 1,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,25</t>
+          <t>1,69; 2,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,36</t>
+          <t>1,29; 1,37</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,75</t>
+          <t>1,38; 1,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,35</t>
         </is>
       </c>
     </row>
@@ -716,42 +716,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,8</t>
+          <t>0,54; 0,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,42</t>
+          <t>0,95; 1,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,01</t>
+          <t>0,77; 1,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,42</t>
+          <t>1,08; 1,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,25</t>
+          <t>0,92; 1,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,75</t>
+          <t>1,4; 1,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,55</t>
+          <t>1,2; 1,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,7</t>
+          <t>1,35; 1,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,54</t>
+          <t>1,21; 1,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,24</t>
+          <t>1,02; 1,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,49</t>
+          <t>1,25; 1,46</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,32</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,74</t>
+          <t>0,54; 0,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,32</t>
+          <t>0,97; 1,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,02</t>
+          <t>0,79; 1,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,24</t>
+          <t>0,92; 1,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,33</t>
+          <t>1,08; 1,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 1,83</t>
+          <t>1,5; 1,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,53</t>
+          <t>1,26; 1,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 1,75</t>
+          <t>1,43; 1,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,0</t>
+          <t>0,84; 1,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,51</t>
+          <t>1,28; 1,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,23</t>
+          <t>1,06; 1,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 1,44</t>
+          <t>1,21; 1,44</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>2,01</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,77</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,71</t>
+          <t>0,48; 0,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,27</t>
+          <t>0,97; 1,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 0,99</t>
+          <t>0,77; 0,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,72</t>
+          <t>1,33; 1,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,14</t>
+          <t>0,92; 1,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 1,8</t>
+          <t>1,47; 1,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,33</t>
+          <t>1,04; 1,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,2</t>
+          <t>1,83; 2,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 0,89</t>
+          <t>0,73; 0,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,49</t>
+          <t>1,27; 1,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,11</t>
+          <t>0,92; 1,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 1,9</t>
+          <t>1,65; 1,93</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,55</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,76</t>
+          <t>0,56; 0,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,13</t>
+          <t>0,84; 1,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,32</t>
+          <t>1,05; 1,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,65</t>
+          <t>1,11; 1,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,37 +1161,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,14</t>
+          <t>1,74; 2,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,01</t>
+          <t>1,63; 2,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,83</t>
+          <t>1,6; 1,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 0,97</t>
+          <t>0,81; 0,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,59</t>
+          <t>1,33; 1,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,63</t>
+          <t>1,39; 1,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 1,66</t>
+          <t>1,42; 1,68</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,43</t>
+          <t>1,52</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,89</t>
+          <t>0,62; 0,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,46</t>
+          <t>0,97; 1,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,98</t>
+          <t>0,65; 0,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,39</t>
+          <t>0,9; 1,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,59</t>
+          <t>1,15; 1,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 2,8</t>
+          <t>2,15; 2,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,82</t>
+          <t>1,32; 1,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,05</t>
+          <t>1,7; 2,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,19</t>
+          <t>0,92; 1,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,05</t>
+          <t>1,62; 2,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,35</t>
+          <t>1,04; 1,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,68</t>
+          <t>1,39; 1,69</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,74</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -1416,52 +1416,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,79</t>
+          <t>0,56; 0,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,35</t>
+          <t>1,04; 1,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,05</t>
+          <t>0,74; 1,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,98</t>
+          <t>1,47; 1,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,31</t>
+          <t>1,01; 1,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,86</t>
+          <t>1,51; 1,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,6</t>
+          <t>1,16; 1,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,29</t>
+          <t>1,84; 2,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,02</t>
+          <t>0,81; 1,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,57</t>
+          <t>1,31; 1,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,06</t>
+          <t>1,72; 2,03</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>1,64</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,87</t>
+          <t>0,64; 0,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,12</t>
+          <t>0,89; 1,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,01</t>
+          <t>0,79; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,43</t>
+          <t>1,2; 1,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,2</t>
+          <t>0,99; 1,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,62</t>
+          <t>1,37; 1,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,34</t>
+          <t>1,1; 1,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,22</t>
+          <t>1,8; 2,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,0</t>
+          <t>0,84; 1,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,33</t>
+          <t>1,16; 1,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,14</t>
+          <t>0,98; 1,15</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,66</t>
+          <t>1,55; 1,75</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,23</t>
         </is>
       </c>
     </row>
@@ -1696,47 +1696,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 0,97</t>
+          <t>0,78; 0,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,91</t>
+          <t>0,71; 0,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,01</t>
+          <t>0,84; 1,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,01</t>
+          <t>0,84; 1,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,29</t>
+          <t>1,08; 1,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,5</t>
+          <t>1,24; 1,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,56</t>
+          <t>1,31; 1,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,7</t>
+          <t>1,37; 1,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,1</t>
+          <t>0,96; 1,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,31</t>
+          <t>1,15; 1,32</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,07</t>
+          <t>0,97; 1,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 0,96</t>
+          <t>0,88; 0,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,26</t>
+          <t>1,17; 1,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,19</t>
+          <t>1,1; 1,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,24</t>
+          <t>1,69; 1,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,37</t>
+          <t>1,28; 1,37</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 1,71</t>
+          <t>1,44; 1,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
+          <t>Población según el número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
